--- a/data/nursery_school/data(2).xlsx
+++ b/data/nursery_school/data(2).xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R115"/>
+  <dimension ref="A1:R120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M17" t="str">
         <v>3か月～</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="str">
         <v>34.229495</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="str">
         <v>34.307041</v>
@@ -1666,7 +1666,7 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="M23" t="str">
         <v>1歳～</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="str">
         <v>34.284657</v>
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="M24" t="str">
         <v>1歳～</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="str">
         <v>34.345964</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="str">
         <v>34.341172</v>
@@ -1857,25 +1857,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="str">
-        <v>34.358509</v>
+        <v>34.2577048673876</v>
       </c>
       <c r="C27" t="str">
-        <v>133.967533</v>
+        <v>134.037076028654</v>
       </c>
       <c r="D27" t="str">
-        <v>高松市下笠居こども園</v>
+        <v>高松市浅野こども園</v>
       </c>
       <c r="E27" t="str">
-        <v>高松市生島町335</v>
+        <v>高松市浅野816-2</v>
       </c>
       <c r="F27" t="str">
-        <v>087-881-2515</v>
+        <v>087-889-2416</v>
       </c>
       <c r="G27" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h142</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h329/</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1890,7 +1890,7 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>1号認定 40、2・3号認定 105</v>
+        <v>1号認定 30、2・3号認定 144</v>
       </c>
       <c r="M27" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -1902,36 +1902,36 @@
         <v>07:30</v>
       </c>
       <c r="P27" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q27" t="str">
         <v/>
       </c>
       <c r="R27" t="str">
-        <v>有</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="str">
-        <v>34.328643</v>
+        <v>34.358509</v>
       </c>
       <c r="C28" t="str">
-        <v>134.156038</v>
+        <v>133.967533</v>
       </c>
       <c r="D28" t="str">
-        <v>高松市はらこども園</v>
+        <v>高松市下笠居こども園</v>
       </c>
       <c r="E28" t="str">
-        <v>高松市牟礼町原570-1</v>
+        <v>高松市生島町335</v>
       </c>
       <c r="F28" t="str">
-        <v>087-845-0234</v>
+        <v>087-881-2515</v>
       </c>
       <c r="G28" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h143</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h142</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1946,7 +1946,7 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>1号認定 90、2・3号認定 138</v>
+        <v>1号認定 40、2・3号認定 105</v>
       </c>
       <c r="M28" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -1958,7 +1958,7 @@
         <v>07:30</v>
       </c>
       <c r="P28" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -1969,25 +1969,25 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="str">
-        <v>34.385761</v>
+        <v>34.328643</v>
       </c>
       <c r="C29" t="str">
-        <v>134.131516</v>
+        <v>134.156038</v>
       </c>
       <c r="D29" t="str">
-        <v>高松市庵治こども園</v>
+        <v>高松市はらこども園</v>
       </c>
       <c r="E29" t="str">
-        <v>高松市庵治町853-1</v>
+        <v>高松市牟礼町原570-1</v>
       </c>
       <c r="F29" t="str">
-        <v>087-871-2535</v>
+        <v>087-845-0234</v>
       </c>
       <c r="G29" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h144</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h143</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>1号認定 45、2・3号認定 105</v>
+        <v>1号認定 63、2・3号認定 165</v>
       </c>
       <c r="M29" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2014,7 +2014,7 @@
         <v>07:30</v>
       </c>
       <c r="P29" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q29" t="str">
         <v/>
@@ -2025,25 +2025,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="str">
-        <v>34.242096</v>
+        <v>34.385761</v>
       </c>
       <c r="C30" t="str">
-        <v>134.005834</v>
+        <v>134.131516</v>
       </c>
       <c r="D30" t="str">
-        <v>高松市香南こども園</v>
+        <v>高松市庵治こども園</v>
       </c>
       <c r="E30" t="str">
-        <v>高松市香南町横井865-1</v>
+        <v>高松市庵治町853-1</v>
       </c>
       <c r="F30" t="str">
-        <v>087-887-7876</v>
+        <v>087-871-2535</v>
       </c>
       <c r="G30" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h145</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h144</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -2058,7 +2058,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>1号認定 90、2・3号認定 179</v>
+        <v>1号認定 45、2・3号認定 105</v>
       </c>
       <c r="M30" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2070,7 +2070,7 @@
         <v>07:30</v>
       </c>
       <c r="P30" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q30" t="str">
         <v/>
@@ -2081,25 +2081,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="str">
-        <v>34.188524</v>
+        <v>34.242096</v>
       </c>
       <c r="C31" t="str">
-        <v>134.061382</v>
+        <v>134.005834</v>
       </c>
       <c r="D31" t="str">
-        <v>高松市塩江こども園</v>
+        <v>高松市香南こども園</v>
       </c>
       <c r="E31" t="str">
-        <v>高松市塩江町安原下第1号887</v>
+        <v>高松市香南町横井865-1</v>
       </c>
       <c r="F31" t="str">
-        <v>087-890-2022</v>
+        <v>087-887-7876</v>
       </c>
       <c r="G31" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h146</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h145</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>1号認定 75、2・3号認定 194</v>
       </c>
       <c r="M31" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2137,25 +2137,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="str">
-        <v>34.237755</v>
+        <v>34.188524</v>
       </c>
       <c r="C32" t="str">
-        <v>134.035134</v>
+        <v>134.061382</v>
       </c>
       <c r="D32" t="str">
-        <v>高松市川東こども園</v>
+        <v>高松市塩江こども園</v>
       </c>
       <c r="E32" t="str">
-        <v>高松市香川町川東上1987-4</v>
+        <v>高松市塩江町安原下第1号887</v>
       </c>
       <c r="F32" t="str">
-        <v>087-879-4602</v>
+        <v>087-890-2022</v>
       </c>
       <c r="G32" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h27</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h146</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>1号認定 90、2・3号認定 153</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M32" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2193,25 +2193,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="str">
-        <v>34.342609</v>
+        <v>34.237755</v>
       </c>
       <c r="C33" t="str">
-        <v>134.099868</v>
+        <v>134.035134</v>
       </c>
       <c r="D33" t="str">
-        <v>屋島こども園</v>
+        <v>高松市川東こども園</v>
       </c>
       <c r="E33" t="str">
-        <v>高松市屋島西町1744-1</v>
+        <v>高松市香川町川東上1987-4</v>
       </c>
       <c r="F33" t="str">
-        <v>087-841-9711</v>
+        <v>087-879-4602</v>
       </c>
       <c r="G33" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h307/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h27</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>1号認定 9、2・3号認定 135</v>
+        <v>1号認定 75、2・3号認定 168</v>
       </c>
       <c r="M33" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2249,25 +2249,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="str">
-        <v>34.2959789</v>
+        <v>34.342609</v>
       </c>
       <c r="C34" t="str">
-        <v>134.0789659</v>
+        <v>134.099868</v>
       </c>
       <c r="D34" t="str">
-        <v>林こども園</v>
+        <v>高松市屋島こども園</v>
       </c>
       <c r="E34" t="str">
-        <v>高松市林町1405-4</v>
+        <v>高松市屋島西町1744-1</v>
       </c>
       <c r="F34" t="str">
-        <v>087-865-1676</v>
+        <v>087-841-9711</v>
       </c>
       <c r="G34" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h306/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h307/</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -2282,7 +2282,7 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>1号認定 105、2・3号認定 194</v>
+        <v>1号認定 9、2・3号認定 135</v>
       </c>
       <c r="M34" t="str">
         <v>1号認定 3歳児～、2・3号認定 3か月～</v>
@@ -2305,31 +2305,31 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="str">
-        <v>34.420292</v>
+        <v>34.2959789</v>
       </c>
       <c r="C35" t="str">
-        <v>134.057016</v>
+        <v>134.0789659</v>
       </c>
       <c r="D35" t="str">
-        <v>高松市小規模保育事業所男木保育所</v>
+        <v>高松市林こども園</v>
       </c>
       <c r="E35" t="str">
-        <v>高松市男木町165</v>
+        <v>高松市林町1405-4</v>
       </c>
       <c r="F35" t="str">
-        <v>087-873-0614</v>
+        <v>087-865-1676</v>
       </c>
       <c r="G35" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%25E9%25AB%2598%25E6%259D%25BE%25E5%25B8%2582%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E4%25BA%258B%25E6%25A5%25AD%25E6%2589%2580%25E3%2580%2580%25E7%2594%25B7%25E6%259C%25A8%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25EF%25BC%2592/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h306/</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>小規模保育施設</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -2338,54 +2338,54 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>6</v>
+        <v>1号認定 90、2・3号認定 209</v>
       </c>
       <c r="M35" t="str">
-        <v>1歳児～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N35" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O35" t="str">
-        <v>09:00</v>
+        <v>07:30</v>
       </c>
       <c r="P35" t="str">
-        <v>16:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q35" t="str">
         <v/>
       </c>
       <c r="R35" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B36" t="str">
-        <v>34.327973</v>
+        <v>34.2768847651024</v>
       </c>
       <c r="C36" t="str">
-        <v>134.058101</v>
+        <v>134.091508945175</v>
       </c>
       <c r="D36" t="str">
-        <v>こぶし今里保育園</v>
+        <v>高松市川島こども園</v>
       </c>
       <c r="E36" t="str">
-        <v>高松市今里町一丁目7-2</v>
+        <v>高松市川島東町253-4</v>
       </c>
       <c r="F36" t="str">
-        <v>087-834-1946</v>
+        <v>087-848-1978</v>
       </c>
       <c r="G36" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h159/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h328/</v>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -2394,16 +2394,16 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>90</v>
+        <v>1号認定 60、2・3号認定 169</v>
       </c>
       <c r="M36" t="str">
-        <v>2か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N36" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O36" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P36" t="str">
         <v>19:00</v>
@@ -2412,36 +2412,36 @@
         <v/>
       </c>
       <c r="R36" t="str">
-        <v>有</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B37" t="str">
-        <v>34.333037</v>
+        <v>34.420292</v>
       </c>
       <c r="C37" t="str">
-        <v>134.051372</v>
+        <v>134.057016</v>
       </c>
       <c r="D37" t="str">
-        <v>敬愛保育園</v>
+        <v>高松市小規模保育事業所男木保育所</v>
       </c>
       <c r="E37" t="str">
-        <v>高松市藤塚町三丁目18-2</v>
+        <v>高松市男木町165</v>
       </c>
       <c r="F37" t="str">
-        <v>087-831-6778</v>
+        <v>087-873-0614</v>
       </c>
       <c r="G37" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h33/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/%25E9%25AB%2598%25E6%259D%25BE%25E5%25B8%2582%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E4%25BA%258B%25E6%25A5%25AD%25E6%2589%2580%25E3%2580%2580%25E7%2594%25B7%25E6%259C%25A8%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25EF%25BC%2592/</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>認定私立保育所</v>
+        <v>小規模保育施設</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2450,19 +2450,19 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M37" t="str">
-        <v>3か月～</v>
+        <v>1歳児～</v>
       </c>
       <c r="N37" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O37" t="str">
-        <v>07:00</v>
+        <v>09:00</v>
       </c>
       <c r="P37" t="str">
-        <v>19:00</v>
+        <v>16:00</v>
       </c>
       <c r="Q37" t="str">
         <v/>
@@ -2473,25 +2473,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B38" t="str">
-        <v>34.328268</v>
+        <v>34.327973</v>
       </c>
       <c r="C38" t="str">
-        <v>134.066087</v>
+        <v>134.058101</v>
       </c>
       <c r="D38" t="str">
-        <v>平安保育園</v>
+        <v>こぶし今里保育園</v>
       </c>
       <c r="E38" t="str">
-        <v>高松市上福岡町894-8</v>
+        <v>高松市今里町一丁目7-2</v>
       </c>
       <c r="F38" t="str">
-        <v>087-833-7734</v>
+        <v>087-834-1946</v>
       </c>
       <c r="G38" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h160/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h159/</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -2506,7 +2506,7 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="M38" t="str">
         <v>2か月～</v>
@@ -2524,30 +2524,30 @@
         <v/>
       </c>
       <c r="R38" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B39" t="str">
-        <v>34.304804</v>
+        <v>34.333037</v>
       </c>
       <c r="C39" t="str">
-        <v>134.02164</v>
+        <v>134.051372</v>
       </c>
       <c r="D39" t="str">
-        <v>勅使百華保育園</v>
+        <v>敬愛保育園</v>
       </c>
       <c r="E39" t="str">
-        <v>高松市勅使町955</v>
+        <v>高松市藤塚町三丁目18-2</v>
       </c>
       <c r="F39" t="str">
-        <v>087-865-2998</v>
+        <v>087-831-6778</v>
       </c>
       <c r="G39" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h34/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h33/</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2562,7 +2562,7 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="M39" t="str">
         <v>3か月～</v>
@@ -2585,25 +2585,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B40" t="str">
-        <v>34.316835</v>
+        <v>34.328268</v>
       </c>
       <c r="C40" t="str">
-        <v>134.024336</v>
+        <v>134.066087</v>
       </c>
       <c r="D40" t="str">
-        <v>西春日保育所</v>
+        <v>平安保育園</v>
       </c>
       <c r="E40" t="str">
-        <v>高松市西春日町1407</v>
+        <v>高松市上福岡町894-8</v>
       </c>
       <c r="F40" t="str">
-        <v>087-866-4166</v>
+        <v>087-833-7734</v>
       </c>
       <c r="G40" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h161/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h160/</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2636,36 +2636,36 @@
         <v/>
       </c>
       <c r="R40" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B41" t="str">
-        <v>34.304304</v>
+        <v>34.304804</v>
       </c>
       <c r="C41" t="str">
-        <v>134.037996</v>
+        <v>134.02164</v>
       </c>
       <c r="D41" t="str">
-        <v>太田西保育園</v>
+        <v>幼保連携型認定こども園　勅使百華こども園</v>
       </c>
       <c r="E41" t="str">
-        <v>高松市太田下町2025</v>
+        <v>高松市勅使町955</v>
       </c>
       <c r="F41" t="str">
-        <v>087-865-0601</v>
+        <v>087-865-2998</v>
       </c>
       <c r="G41" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h162/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h340/</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2674,10 +2674,10 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>100</v>
+        <v>1号認定 15、2・3号認定 220</v>
       </c>
       <c r="M41" t="str">
-        <v>2か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N41" t="str">
         <v>月火水木金土</v>
@@ -2692,30 +2692,30 @@
         <v/>
       </c>
       <c r="R41" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B42" t="str">
-        <v>34.309654</v>
+        <v>34.316835</v>
       </c>
       <c r="C42" t="str">
-        <v>134.0631</v>
+        <v>134.024336</v>
       </c>
       <c r="D42" t="str">
-        <v>こぶし中央保育園</v>
+        <v>西春日保育所</v>
       </c>
       <c r="E42" t="str">
-        <v>高松市木太町5089-9</v>
+        <v>高松市西春日町1407</v>
       </c>
       <c r="F42" t="str">
-        <v>087-866-7169</v>
+        <v>087-866-4166</v>
       </c>
       <c r="G42" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h35/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h161/</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -2730,7 +2730,7 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="M42" t="str">
         <v>2か月～</v>
@@ -2753,25 +2753,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B43" t="str">
-        <v>34.350107</v>
+        <v>34.304304</v>
       </c>
       <c r="C43" t="str">
-        <v>134.091559</v>
+        <v>134.037996</v>
       </c>
       <c r="D43" t="str">
-        <v>あすなろ保育園</v>
+        <v>らく楽太田保育園</v>
       </c>
       <c r="E43" t="str">
-        <v>高松市屋島西町2453-6</v>
+        <v>高松市太田下町2025</v>
       </c>
       <c r="F43" t="str">
-        <v>087-843-3143</v>
+        <v>087-865-0601</v>
       </c>
       <c r="G43" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h36/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h162/</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="M43" t="str">
         <v>3か月～</v>
@@ -2798,7 +2798,7 @@
         <v>07:00</v>
       </c>
       <c r="P43" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q43" t="str">
         <v/>
@@ -2809,25 +2809,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B44" t="str">
-        <v>34.300415</v>
+        <v>34.309654</v>
       </c>
       <c r="C44" t="str">
-        <v>134.115798</v>
+        <v>134.0631</v>
       </c>
       <c r="D44" t="str">
-        <v>西光寺保育所</v>
+        <v>こぶし中央保育園</v>
       </c>
       <c r="E44" t="str">
-        <v>高松市前田西町167-1</v>
+        <v>高松市木太町5089-9</v>
       </c>
       <c r="F44" t="str">
-        <v>087-847-6237</v>
+        <v>087-866-7169</v>
       </c>
       <c r="G44" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h164/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h35/</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -2842,7 +2842,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="M44" t="str">
         <v>2か月～</v>
@@ -2865,25 +2865,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B45" t="str">
-        <v>34.299537</v>
+        <v>34.350107</v>
       </c>
       <c r="C45" t="str">
-        <v>134.092378</v>
+        <v>134.091559</v>
       </c>
       <c r="D45" t="str">
-        <v>川添保育園</v>
+        <v>あすなろ保育園</v>
       </c>
       <c r="E45" t="str">
-        <v>高松市下田井町52</v>
+        <v>高松市屋島西町2453-6</v>
       </c>
       <c r="F45" t="str">
-        <v>087-847-5078</v>
+        <v>087-843-3143</v>
       </c>
       <c r="G45" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h165/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h36/</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -2898,7 +2898,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="M45" t="str">
         <v>3か月～</v>
@@ -2921,31 +2921,31 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B46" t="str">
-        <v>34.277465</v>
+        <v>34.300415</v>
       </c>
       <c r="C46" t="str">
-        <v>134.030037</v>
+        <v>134.115798</v>
       </c>
       <c r="D46" t="str">
-        <v>高松南保育園</v>
+        <v>認定こども園　西光寺保育園</v>
       </c>
       <c r="E46" t="str">
-        <v>高松市寺井町453-1</v>
+        <v>高松市前田西町167-1</v>
       </c>
       <c r="F46" t="str">
-        <v>087-886-0275</v>
+        <v>087-847-6237</v>
       </c>
       <c r="G46" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h38/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h330/</v>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2954,10 +2954,10 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>160</v>
+        <v>1号認定 15、2・3号認定 107</v>
       </c>
       <c r="M46" t="str">
-        <v>6か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
       </c>
       <c r="N46" t="str">
         <v>月火水木金土</v>
@@ -2977,31 +2977,31 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B47" t="str">
-        <v>34.284927</v>
+        <v>34.299537</v>
       </c>
       <c r="C47" t="str">
-        <v>134.010137</v>
+        <v>134.092378</v>
       </c>
       <c r="D47" t="str">
-        <v>円座百華保育園</v>
+        <v>幼保連携型認定こども園　川添こども園</v>
       </c>
       <c r="E47" t="str">
-        <v>高松市円座町1478-1</v>
+        <v>高松市下田井町52</v>
       </c>
       <c r="F47" t="str">
-        <v>087-885-1203</v>
+        <v>087-847-5078</v>
       </c>
       <c r="G47" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h167/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h331/</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -3010,10 +3010,10 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>260</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M47" t="str">
-        <v>7か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N47" t="str">
         <v>月火水木金土</v>
@@ -3033,25 +3033,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B48" t="str">
-        <v>34.306205</v>
+        <v>34.277465</v>
       </c>
       <c r="C48" t="str">
-        <v>133.998614</v>
+        <v>134.030037</v>
       </c>
       <c r="D48" t="str">
-        <v>高松西保育園</v>
+        <v>高松南保育園</v>
       </c>
       <c r="E48" t="str">
-        <v>高松市檀紙町1521-4</v>
+        <v>高松市寺井町453-1</v>
       </c>
       <c r="F48" t="str">
-        <v>087-886-5006</v>
+        <v>087-886-0275</v>
       </c>
       <c r="G48" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h40/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h38/</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -3066,10 +3066,10 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="M48" t="str">
-        <v>2か月～</v>
+        <v>6か月～</v>
       </c>
       <c r="N48" t="str">
         <v>月火水木金土</v>
@@ -3089,31 +3089,31 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B49" t="str">
-        <v>34.285075</v>
+        <v>34.284927</v>
       </c>
       <c r="C49" t="str">
-        <v>134.110374</v>
+        <v>134.010137</v>
       </c>
       <c r="D49" t="str">
-        <v>若葉保育園</v>
+        <v>幼保連携型　円座百華こども園</v>
       </c>
       <c r="E49" t="str">
-        <v>高松市亀田南町108-2</v>
+        <v>高松市円座町1478-1</v>
       </c>
       <c r="F49" t="str">
-        <v>087-847-7932</v>
+        <v>087-885-1203</v>
       </c>
       <c r="G49" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h168/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h332/</v>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -3122,10 +3122,10 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>130</v>
+        <v>1号認定 15、2・3号認定 250</v>
       </c>
       <c r="M49" t="str">
-        <v>3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N49" t="str">
         <v>月火水木金土</v>
@@ -3145,25 +3145,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B50" t="str">
-        <v>34.311827</v>
+        <v>34.306205</v>
       </c>
       <c r="C50" t="str">
-        <v>134.08609</v>
+        <v>133.998614</v>
       </c>
       <c r="D50" t="str">
-        <v>白樺保育園</v>
+        <v>高松西保育園</v>
       </c>
       <c r="E50" t="str">
-        <v>高松市元山町855-2</v>
+        <v>高松市檀紙町1521-4</v>
       </c>
       <c r="F50" t="str">
-        <v>087-866-6555</v>
+        <v>087-886-5006</v>
       </c>
       <c r="G50" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h41/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h40/</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M50" t="str">
         <v>3か月～</v>
@@ -3201,25 +3201,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B51" t="str">
-        <v>34.341315</v>
+        <v>34.285075</v>
       </c>
       <c r="C51" t="str">
-        <v>134.06296</v>
+        <v>134.110374</v>
       </c>
       <c r="D51" t="str">
-        <v>松福保育園</v>
+        <v>若葉保育園</v>
       </c>
       <c r="E51" t="str">
-        <v>高松市松福町二丁目18-16</v>
+        <v>高松市亀田南町108-2</v>
       </c>
       <c r="F51" t="str">
-        <v>087-822-7605</v>
+        <v>087-847-7932</v>
       </c>
       <c r="G51" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h42/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h168/</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -3234,10 +3234,10 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M51" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N51" t="str">
         <v>月火水木金土</v>
@@ -3252,30 +3252,30 @@
         <v/>
       </c>
       <c r="R51" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B52" t="str">
-        <v>34.320782</v>
+        <v>34.311827</v>
       </c>
       <c r="C52" t="str">
-        <v>134.067903</v>
+        <v>134.08609</v>
       </c>
       <c r="D52" t="str">
-        <v>さくらんぼ保育園</v>
+        <v>白樺保育園</v>
       </c>
       <c r="E52" t="str">
-        <v>高松市木太町1165-3</v>
+        <v>高松市元山町855-2</v>
       </c>
       <c r="F52" t="str">
-        <v>087-867-4151</v>
+        <v>087-866-6555</v>
       </c>
       <c r="G52" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h43/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h41/</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -3290,16 +3290,16 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="M52" t="str">
-        <v>1歳児～</v>
+        <v>3か月～</v>
       </c>
       <c r="N52" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O52" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P52" t="str">
         <v>19:00</v>
@@ -3313,25 +3313,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" t="str">
-        <v>34.263658</v>
+        <v>34.320782</v>
       </c>
       <c r="C53" t="str">
-        <v>134.108531</v>
+        <v>134.067903</v>
       </c>
       <c r="D53" t="str">
-        <v>すみれ保育園</v>
+        <v>さくらんぼ保育園</v>
       </c>
       <c r="E53" t="str">
-        <v>高松市十川東町556-1</v>
+        <v>高松市木太町1165-3</v>
       </c>
       <c r="F53" t="str">
-        <v>087-848-0806</v>
+        <v>087-867-4151</v>
       </c>
       <c r="G53" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h169/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h43/</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -3346,16 +3346,16 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="M53" t="str">
-        <v>3か月～</v>
+        <v>1歳～</v>
       </c>
       <c r="N53" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O53" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P53" t="str">
         <v>19:00</v>
@@ -3369,25 +3369,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" t="str">
-        <v>34.343745</v>
+        <v>34.263658</v>
       </c>
       <c r="C54" t="str">
-        <v>134.052287</v>
+        <v>134.108531</v>
       </c>
       <c r="D54" t="str">
-        <v>高松第二保育園</v>
+        <v>すみれ保育園</v>
       </c>
       <c r="E54" t="str">
-        <v>高松市御坊町2-2</v>
+        <v>高松市十川東町556-1</v>
       </c>
       <c r="F54" t="str">
-        <v>087-821-5241</v>
+        <v>087-848-0806</v>
       </c>
       <c r="G54" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h44/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h169/</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -3402,48 +3402,48 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="M54" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N54" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O54" t="str">
-        <v>06:40</v>
+        <v>07:00</v>
       </c>
       <c r="P54" t="str">
-        <v>25:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q54" t="str">
         <v/>
       </c>
       <c r="R54" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" t="str">
-        <v>34.327799</v>
+        <v>34.343745</v>
       </c>
       <c r="C55" t="str">
-        <v>134.062199</v>
+        <v>134.052287</v>
       </c>
       <c r="D55" t="str">
-        <v>今里保育所</v>
+        <v>高松第二保育園</v>
       </c>
       <c r="E55" t="str">
-        <v>高松市今里町二丁目1-5</v>
+        <v>高松市御坊町2-2</v>
       </c>
       <c r="F55" t="str">
-        <v>087-834-3535</v>
+        <v>087-821-5241</v>
       </c>
       <c r="G55" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h45/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h44/</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -3458,19 +3458,19 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="M55" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N55" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O55" t="str">
-        <v>07:00</v>
+        <v>8:00</v>
       </c>
       <c r="P55" t="str">
-        <v>19:00</v>
+        <v>26:00</v>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -3481,25 +3481,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" t="str">
-        <v>34.25728</v>
+        <v>34.327799</v>
       </c>
       <c r="C56" t="str">
-        <v>134.035674</v>
+        <v>134.062199</v>
       </c>
       <c r="D56" t="str">
-        <v>さんさん保育園</v>
+        <v>今里保育所</v>
       </c>
       <c r="E56" t="str">
-        <v>高松市香川町浅野834-1</v>
+        <v>高松市今里町二丁目1-5</v>
       </c>
       <c r="F56" t="str">
-        <v>087-888-6333</v>
+        <v>087-834-3535</v>
       </c>
       <c r="G56" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h170/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h45/</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -3514,7 +3514,7 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="M56" t="str">
         <v>3か月～</v>
@@ -3532,36 +3532,36 @@
         <v/>
       </c>
       <c r="R56" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" t="str">
-        <v>34.289495</v>
+        <v>34.25728</v>
       </c>
       <c r="C57" t="str">
-        <v>133.952485</v>
+        <v>134.035674</v>
       </c>
       <c r="D57" t="str">
-        <v>みよし保育園</v>
+        <v>さんさんこども園</v>
       </c>
       <c r="E57" t="str">
-        <v>高松市国分寺町柏原80</v>
+        <v>高松市香川町浅野834-1</v>
       </c>
       <c r="F57" t="str">
-        <v>087-874-0622</v>
+        <v>087-888-6333</v>
       </c>
       <c r="G57" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h171/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h357/</v>
       </c>
       <c r="H57" t="str">
         <v/>
       </c>
       <c r="I57" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>80</v>
+        <v>1号認定 10、2・3号認定 120</v>
       </c>
       <c r="M57" t="str">
-        <v>3か月～</v>
+        <v>1号認定 3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N57" t="str">
         <v>月火水木金土</v>
@@ -3588,30 +3588,30 @@
         <v/>
       </c>
       <c r="R57" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="str">
-        <v>34.274113</v>
+        <v>34.289495</v>
       </c>
       <c r="C58" t="str">
-        <v>133.973116</v>
+        <v>133.952485</v>
       </c>
       <c r="D58" t="str">
-        <v>みのり保育園</v>
+        <v>らく楽国分寺保育園</v>
       </c>
       <c r="E58" t="str">
-        <v>高松市国分寺町福家甲1982</v>
+        <v>高松市国分寺町柏原80</v>
       </c>
       <c r="F58" t="str">
-        <v>087-874-4309</v>
+        <v>087-874-0622</v>
       </c>
       <c r="G58" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h172/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h171/</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -3626,7 +3626,7 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M58" t="str">
         <v>3か月～</v>
@@ -3644,30 +3644,30 @@
         <v/>
       </c>
       <c r="R58" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" t="str">
-        <v>34.337967</v>
+        <v>34.274113</v>
       </c>
       <c r="C59" t="str">
-        <v>134.130825</v>
+        <v>133.973116</v>
       </c>
       <c r="D59" t="str">
-        <v>八栗保育所</v>
+        <v>みのり保育園</v>
       </c>
       <c r="E59" t="str">
-        <v>高松市牟礼町牟礼401</v>
+        <v>高松市国分寺町福家甲1982</v>
       </c>
       <c r="F59" t="str">
-        <v>087-845-0033</v>
+        <v>087-874-4309</v>
       </c>
       <c r="G59" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h173/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h172/</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -3682,19 +3682,19 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="M59" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N59" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O59" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P59" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q59" t="str">
         <v/>
@@ -3705,25 +3705,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" t="str">
-        <v>34.347055</v>
+        <v>34.337967</v>
       </c>
       <c r="C60" t="str">
-        <v>134.055965</v>
+        <v>134.130825</v>
       </c>
       <c r="D60" t="str">
-        <v>城東保育園</v>
+        <v>八栗保育所</v>
       </c>
       <c r="E60" t="str">
-        <v>高松市城東町一丁目1-45</v>
+        <v>高松市牟礼町牟礼401</v>
       </c>
       <c r="F60" t="str">
-        <v>087-822-1340</v>
+        <v>087-845-0033</v>
       </c>
       <c r="G60" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h46/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h173/</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -3738,7 +3738,7 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="M60" t="str">
         <v>2か月～</v>
@@ -3750,7 +3750,7 @@
         <v>07:30</v>
       </c>
       <c r="P60" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q60" t="str">
         <v/>
@@ -3761,25 +3761,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" t="str">
-        <v>34.334252</v>
+        <v>34.347055</v>
       </c>
       <c r="C61" t="str">
-        <v>134.057679</v>
+        <v>134.055965</v>
       </c>
       <c r="D61" t="str">
-        <v>こぶし花園保育園</v>
+        <v>城東保育園</v>
       </c>
       <c r="E61" t="str">
-        <v>高松市花園町一丁目9-32</v>
+        <v>高松市城東町一丁目1-45</v>
       </c>
       <c r="F61" t="str">
-        <v>087-831-5136</v>
+        <v>087-822-1340</v>
       </c>
       <c r="G61" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h47/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h46/</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M61" t="str">
         <v>2か月～</v>
@@ -3812,36 +3812,36 @@
         <v/>
       </c>
       <c r="R61" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" t="str">
-        <v>0</v>
+        <v>34.334252</v>
       </c>
       <c r="C62" t="str">
-        <v>0</v>
+        <v>134.057679</v>
       </c>
       <c r="D62" t="str">
-        <v/>
+        <v>こぶし花園保育園</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>高松市花園町一丁目9-32</v>
       </c>
       <c r="F62" t="str">
-        <v/>
+        <v>087-831-5136</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h47/</v>
       </c>
       <c r="H62" t="str">
         <v/>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>認定私立保育所</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -3850,54 +3850,54 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v/>
+        <v>90</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>2か月～</v>
       </c>
       <c r="N62" t="str">
-        <v/>
+        <v>月火水木金土</v>
       </c>
       <c r="O62" t="str">
-        <v/>
+        <v>07:30</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>19:00</v>
       </c>
       <c r="Q62" t="str">
         <v/>
       </c>
       <c r="R62" t="str">
-        <v/>
+        <v>無</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" t="str">
-        <v>34.287693</v>
+        <v>0</v>
       </c>
       <c r="C63" t="str">
-        <v>134.05974</v>
+        <v>0</v>
       </c>
       <c r="D63" t="str">
-        <v>れんげ保育園</v>
+        <v/>
       </c>
       <c r="E63" t="str">
-        <v>高松市多肥上町2390-1</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v>087-888-8080</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h49/</v>
+        <v/>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>認定私立保育所</v>
+        <v/>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -3906,48 +3906,48 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>90</v>
+        <v/>
       </c>
       <c r="M63" t="str">
-        <v>3か月～</v>
+        <v/>
       </c>
       <c r="N63" t="str">
-        <v>月火水木金土</v>
+        <v/>
       </c>
       <c r="O63" t="str">
-        <v>07:00</v>
+        <v/>
       </c>
       <c r="P63" t="str">
-        <v>19:00</v>
+        <v/>
       </c>
       <c r="Q63" t="str">
         <v/>
       </c>
       <c r="R63" t="str">
-        <v>無</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" t="str">
-        <v>34.308543</v>
+        <v>34.287693</v>
       </c>
       <c r="C64" t="str">
-        <v>134.056433</v>
+        <v>134.05974</v>
       </c>
       <c r="D64" t="str">
-        <v>さくら伏石保育園</v>
+        <v>れんげ保育園</v>
       </c>
       <c r="E64" t="str">
-        <v>高松市伏石町2135-3</v>
+        <v>高松市多肥上町2390-1</v>
       </c>
       <c r="F64" t="str">
-        <v>087-867-1100</v>
+        <v>087-888-8080</v>
       </c>
       <c r="G64" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h50/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h49/</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -3974,7 +3974,7 @@
         <v>07:00</v>
       </c>
       <c r="P64" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q64" t="str">
         <v/>
@@ -3985,25 +3985,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" t="str">
-        <v>34.323827</v>
+        <v>34.308543</v>
       </c>
       <c r="C65" t="str">
-        <v>134.092254</v>
+        <v>134.056433</v>
       </c>
       <c r="D65" t="str">
-        <v>らく楽保育園</v>
+        <v>さくら伏石保育園</v>
       </c>
       <c r="E65" t="str">
-        <v>高松市春日町483-1</v>
+        <v>高松市伏石町2135-3</v>
       </c>
       <c r="F65" t="str">
-        <v>087-844-0111</v>
+        <v>087-867-1100</v>
       </c>
       <c r="G65" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h51/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h50/</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -4018,7 +4018,7 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="M65" t="str">
         <v>3か月～</v>
@@ -4027,10 +4027,10 @@
         <v>月火水木金土</v>
       </c>
       <c r="O65" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P65" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="Q65" t="str">
         <v/>
@@ -4041,25 +4041,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" t="str">
-        <v>34.349557</v>
+        <v>34.323827</v>
       </c>
       <c r="C66" t="str">
-        <v>134.003925</v>
+        <v>134.092254</v>
       </c>
       <c r="D66" t="str">
-        <v>初音保育所</v>
+        <v>らく楽保育園</v>
       </c>
       <c r="E66" t="str">
-        <v>高松市香西本町17-1</v>
+        <v>高松市春日町483-1</v>
       </c>
       <c r="F66" t="str">
-        <v>087-813-3258</v>
+        <v>087-844-0111</v>
       </c>
       <c r="G66" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h52/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h51/</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -4074,13 +4074,13 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="M66" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N66" t="str">
-        <v>月火水木金土日</v>
+        <v>月火水木金土</v>
       </c>
       <c r="O66" t="str">
         <v>07:30</v>
@@ -4092,30 +4092,30 @@
         <v/>
       </c>
       <c r="R66" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" t="str">
-        <v>34.308532</v>
+        <v>34.349557</v>
       </c>
       <c r="C67" t="str">
-        <v>134.067283</v>
+        <v>134.003925</v>
       </c>
       <c r="D67" t="str">
-        <v>さくら木太保育園</v>
+        <v>初音保育所</v>
       </c>
       <c r="E67" t="str">
-        <v>高松市木太町5113-15</v>
+        <v>高松市香西本町17-1</v>
       </c>
       <c r="F67" t="str">
-        <v>087-802-8080</v>
+        <v>087-813-3258</v>
       </c>
       <c r="G67" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h260/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h52/</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="M67" t="str">
         <v>3か月～</v>
@@ -4139,45 +4139,45 @@
         <v>月火水木金土</v>
       </c>
       <c r="O67" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P67" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q67" t="str">
         <v/>
       </c>
       <c r="R67" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" t="str">
-        <v>0</v>
+        <v>34.308532</v>
       </c>
       <c r="C68" t="str">
-        <v>0</v>
+        <v>134.067283</v>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>さくら木太保育園</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>高松市木太町5113-15</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>087-802-8080</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h260/</v>
       </c>
       <c r="H68" t="str">
         <v/>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>認定私立保育所</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -4186,54 +4186,54 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v/>
+        <v>99</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>3か月～</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>月火水木金土</v>
       </c>
       <c r="O68" t="str">
-        <v/>
+        <v>07:00</v>
       </c>
       <c r="P68" t="str">
-        <v/>
+        <v>20:00</v>
       </c>
       <c r="Q68" t="str">
         <v/>
       </c>
       <c r="R68" t="str">
-        <v/>
+        <v>無</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69" t="str">
-        <v>34.333051</v>
+        <v>0</v>
       </c>
       <c r="C69" t="str">
-        <v>134.055788</v>
+        <v>0</v>
       </c>
       <c r="D69" t="str">
-        <v>高松くりの木保育園</v>
+        <v/>
       </c>
       <c r="E69" t="str">
-        <v>高松市花園町三丁目4-5</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v>087-880-7211</v>
+        <v/>
       </c>
       <c r="G69" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h268/</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>認定私立保育所</v>
+        <v/>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -4242,54 +4242,54 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>105</v>
+        <v/>
       </c>
       <c r="M69" t="str">
-        <v>3か月～</v>
+        <v/>
       </c>
       <c r="N69" t="str">
-        <v>月火水木金土</v>
+        <v/>
       </c>
       <c r="O69" t="str">
-        <v>07:00</v>
+        <v/>
       </c>
       <c r="P69" t="str">
-        <v>19:00</v>
+        <v/>
       </c>
       <c r="Q69" t="str">
         <v/>
       </c>
       <c r="R69" t="str">
-        <v>無</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" t="str">
-        <v>34.343232</v>
+        <v>34.333051</v>
       </c>
       <c r="C70" t="str">
-        <v>134.065675</v>
+        <v>134.055788</v>
       </c>
       <c r="D70" t="str">
-        <v>らく楽第二保育園</v>
+        <v>認定こども園　高松くりの木学舎</v>
       </c>
       <c r="E70" t="str">
-        <v>高松市松福町二丁目4-4</v>
+        <v>高松市花園町三丁目4-5</v>
       </c>
       <c r="F70" t="str">
-        <v>087-826-0111</v>
+        <v>087-880-7211</v>
       </c>
       <c r="G70" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h269/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h333/</v>
       </c>
       <c r="H70" t="str">
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -4298,16 +4298,16 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>72</v>
+        <v>1号認定 9、2・3号認定 96</v>
       </c>
       <c r="M70" t="str">
-        <v>3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N70" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O70" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P70" t="str">
         <v>19:00</v>
@@ -4316,30 +4316,30 @@
         <v/>
       </c>
       <c r="R70" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" t="str">
-        <v>34.291607</v>
+        <v>34.343232</v>
       </c>
       <c r="C71" t="str">
-        <v>134.075471</v>
+        <v>134.065675</v>
       </c>
       <c r="D71" t="str">
-        <v>あさがお保育園</v>
+        <v>らく楽第二保育園</v>
       </c>
       <c r="E71" t="str">
-        <v>高松市上林町69</v>
+        <v>高松市松福町二丁目4-4</v>
       </c>
       <c r="F71" t="str">
-        <v>087-899-5660</v>
+        <v>087-826-0111</v>
       </c>
       <c r="G71" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h276/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h269/</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -4354,10 +4354,10 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="M71" t="str">
-        <v>３か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N71" t="str">
         <v>月火水木金土</v>
@@ -4372,36 +4372,36 @@
         <v/>
       </c>
       <c r="R71" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72" t="str">
-        <v>34.3051941</v>
+        <v>34.291607</v>
       </c>
       <c r="C72" t="str">
-        <v>134.0610552</v>
+        <v>134.075471</v>
       </c>
       <c r="D72" t="str">
-        <v>保育園アルペジオ高松多肥下町園</v>
+        <v>認定こども園あさがおこども園</v>
       </c>
       <c r="E72" t="str">
-        <v>高松市多肥下町1524-15</v>
+        <v>高松市上林町69</v>
       </c>
       <c r="F72" t="str">
-        <v>087-802-5583</v>
+        <v>087-899-5660</v>
       </c>
       <c r="G72" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h288/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h358/</v>
       </c>
       <c r="H72" t="str">
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4410,10 +4410,10 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>80</v>
+        <v>1号認定 9、2・3号認定 131</v>
       </c>
       <c r="M72" t="str">
-        <v>6か月</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N72" t="str">
         <v>月火水木金土</v>
@@ -4422,7 +4422,7 @@
         <v>07:30</v>
       </c>
       <c r="P72" t="str">
-        <v>19:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q72" t="str">
         <v/>
@@ -4433,25 +4433,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73" t="str">
-        <v>34.3034175</v>
+        <v>34.3051941</v>
       </c>
       <c r="C73" t="str">
-        <v>134.0533292</v>
+        <v>134.0610552</v>
       </c>
       <c r="D73" t="str">
-        <v>さくら太田保育園</v>
+        <v>保育園アルペジオ高松多肥下町園</v>
       </c>
       <c r="E73" t="str">
-        <v>高松市太田下町3032-1</v>
+        <v>高松市多肥下町1524-15</v>
       </c>
       <c r="F73" t="str">
-        <v>087-868-3700</v>
+        <v>087-802-5583</v>
       </c>
       <c r="G73" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h289/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h288/</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -4466,54 +4466,54 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="M73" t="str">
-        <v>3か月</v>
+        <v>満6か月</v>
       </c>
       <c r="N73" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O73" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P73" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q73" t="str">
         <v/>
       </c>
       <c r="R73" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B74" t="str">
-        <v>34.3064057</v>
+        <v>34.3034175</v>
       </c>
       <c r="C74" t="str">
-        <v>134.042294</v>
+        <v>134.0533292</v>
       </c>
       <c r="D74" t="str">
-        <v>にこにこ保育園</v>
+        <v>さくら太田保育園</v>
       </c>
       <c r="E74" t="str">
-        <v>高松市林町294-1</v>
+        <v>高松市太田下町3032-1</v>
       </c>
       <c r="F74" t="str">
-        <v>087-813-8300</v>
+        <v>087-868-3700</v>
       </c>
       <c r="G74" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h308/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h289/</v>
       </c>
       <c r="H74" t="str">
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>認可私立保育所</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4522,48 +4522,48 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="M74" t="str">
-        <v>おおむね2か月～</v>
+        <v>3か月</v>
       </c>
       <c r="N74" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O74" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P74" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="Q74" t="str">
         <v/>
       </c>
       <c r="R74" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" t="str">
-        <v>34.3047038</v>
+        <v>34.3064057</v>
       </c>
       <c r="C75" t="str">
-        <v>134.0565783</v>
+        <v>134.042294</v>
       </c>
       <c r="D75" t="str">
-        <v>あい保育園太田</v>
+        <v>にこにここども園</v>
       </c>
       <c r="E75" t="str">
-        <v>高松市太田下町3027-3</v>
+        <v>高松市林町294-1</v>
       </c>
       <c r="F75" t="str">
-        <v>087-802-9065</v>
+        <v>087-813-8300</v>
       </c>
       <c r="G75" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h312/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h308/</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -4578,48 +4578,48 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M75" t="str">
-        <v>３か月～</v>
+        <v>2か月～</v>
       </c>
       <c r="N75" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O75" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P75" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q75" t="str">
         <v/>
       </c>
       <c r="R75" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B76" t="str">
-        <v>34.3431504</v>
+        <v>34.3047038</v>
       </c>
       <c r="C76" t="str">
-        <v>134.0615252</v>
+        <v>134.0565783</v>
       </c>
       <c r="D76" t="str">
-        <v>さくら福々保育園</v>
+        <v>アイグラン保育園太田</v>
       </c>
       <c r="E76" t="str">
-        <v>高松市松福町一丁目229-55</v>
+        <v>高松市太田下町3027-4</v>
       </c>
       <c r="F76" t="str">
-        <v>087-802-1860</v>
+        <v>087-802-9065</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h312/</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -4634,7 +4634,7 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M76" t="str">
         <v>３か月～</v>
@@ -4657,31 +4657,31 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" t="str">
-        <v>34.292144</v>
+        <v>34.3431504</v>
       </c>
       <c r="C77" t="str">
-        <v>134.066237</v>
+        <v>134.0615252</v>
       </c>
       <c r="D77" t="str">
-        <v>サンシャインこどもの森</v>
+        <v>さくら福々保育園</v>
       </c>
       <c r="E77" t="str">
-        <v>高松市上林町502-2</v>
+        <v>高松市松福町一丁目12-7</v>
       </c>
       <c r="F77" t="str">
-        <v>087-889-8181</v>
+        <v>087-802-1860</v>
       </c>
       <c r="G77" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h147/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h322/</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認可私立保育所</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4690,48 +4690,48 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>96</v>
       </c>
       <c r="M77" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>３か月～</v>
       </c>
       <c r="N77" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O77" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P77" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="Q77" t="str">
         <v/>
       </c>
       <c r="R77" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" t="str">
-        <v>34.303319</v>
+        <v>34.292144</v>
       </c>
       <c r="C78" t="str">
-        <v>133.949144</v>
+        <v>134.066237</v>
       </c>
       <c r="D78" t="str">
-        <v>いずみこども園</v>
+        <v>サンシャインこどもの森</v>
       </c>
       <c r="E78" t="str">
-        <v>高松市国分寺町国分2408</v>
+        <v>高松市上林町502-2</v>
       </c>
       <c r="F78" t="str">
-        <v>087-874-0882</v>
+        <v>087-889-8181</v>
       </c>
       <c r="G78" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h148</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h147/</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -4746,19 +4746,19 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>1号認定 15、2・3号認定 100</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M78" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N78" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O78" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P78" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q78" t="str">
         <v/>
@@ -4769,25 +4769,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79" t="str">
-        <v>34.304328</v>
+        <v>34.303319</v>
       </c>
       <c r="C79" t="str">
-        <v>133.97246</v>
+        <v>133.949144</v>
       </c>
       <c r="D79" t="str">
-        <v>いずみこども園分園</v>
+        <v>いずみこども園</v>
       </c>
       <c r="E79" t="str">
-        <v>高松市国分寺町新居281-1</v>
+        <v>高松市国分寺町国分2408</v>
       </c>
       <c r="F79" t="str">
-        <v>087-875-0882</v>
+        <v>087-874-0882</v>
       </c>
       <c r="G79" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h211</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h148</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -4802,19 +4802,19 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>2・3号認定 20</v>
+        <v>1号認定 15、2・3号認定 85</v>
       </c>
       <c r="M79" t="str">
-        <v>2・3号認定 3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N79" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O79" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P79" t="str">
-        <v>18:30</v>
+        <v>19:30</v>
       </c>
       <c r="Q79" t="str">
         <v/>
@@ -4825,25 +4825,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B80" t="str">
-        <v>34.327571</v>
+        <v>34.304328</v>
       </c>
       <c r="C80" t="str">
-        <v>134.087355</v>
+        <v>133.97246</v>
       </c>
       <c r="D80" t="str">
-        <v>認定こども園高松東幼稚園</v>
+        <v>いずみこども園分園</v>
       </c>
       <c r="E80" t="str">
-        <v>高松市春日町688</v>
+        <v>高松市国分寺町新居281-1</v>
       </c>
       <c r="F80" t="str">
-        <v>087-841-2306</v>
+        <v>087-875-0882</v>
       </c>
       <c r="G80" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h262</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h211</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -4858,48 +4858,48 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>1号認定 284、2・3号認定 166</v>
+        <v>2・3号認定 20</v>
       </c>
       <c r="M80" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>2・3号認定 3か月～２歳児</v>
       </c>
       <c r="N80" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O80" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P80" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q80" t="str">
         <v/>
       </c>
       <c r="R80" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" t="str">
-        <v>34.325356</v>
+        <v>34.327571</v>
       </c>
       <c r="C81" t="str">
-        <v>134.099079</v>
+        <v>134.087355</v>
       </c>
       <c r="D81" t="str">
-        <v>認定こども園新田幼稚園</v>
+        <v>認定こども園高松東幼稚園</v>
       </c>
       <c r="E81" t="str">
-        <v>高松市新田町甲2630-1</v>
+        <v>高松市春日町688</v>
       </c>
       <c r="F81" t="str">
-        <v>087-841-3686</v>
+        <v>087-841-2306</v>
       </c>
       <c r="G81" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h263</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h262</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -4914,16 +4914,16 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>1号認定 75、2・3号認定 57</v>
+        <v>1号認定 284、2・3号認定 166</v>
       </c>
       <c r="M81" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N81" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O81" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P81" t="str">
         <v>19:00</v>
@@ -4932,30 +4932,30 @@
         <v/>
       </c>
       <c r="R81" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" t="str">
-        <v>34.268464</v>
+        <v>34.325356</v>
       </c>
       <c r="C82" t="str">
-        <v>134.006758</v>
+        <v>134.099079</v>
       </c>
       <c r="D82" t="str">
-        <v>認定こども園和光こども園</v>
+        <v>認定こども園新田幼稚園</v>
       </c>
       <c r="E82" t="str">
-        <v>高松市川部町1561-1</v>
+        <v>高松市新田町甲2630-1</v>
       </c>
       <c r="F82" t="str">
-        <v>087-886-5879</v>
+        <v>087-841-3686</v>
       </c>
       <c r="G82" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h39/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h263</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -4970,16 +4970,16 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>1号認定 15、2・3号認定 100</v>
+        <v>1号認定 75、2・3号認定 57</v>
       </c>
       <c r="M82" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N82" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O82" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P82" t="str">
         <v>19:00</v>
@@ -4988,30 +4988,30 @@
         <v/>
       </c>
       <c r="R82" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" t="str">
-        <v>34.331077</v>
+        <v>34.268464</v>
       </c>
       <c r="C83" t="str">
-        <v>134.094275</v>
+        <v>134.006758</v>
       </c>
       <c r="D83" t="str">
-        <v>認定こども園春日こども園</v>
+        <v>認定こども園和光こども園</v>
       </c>
       <c r="E83" t="str">
-        <v>高松市春日町1287-1</v>
+        <v>高松市川部町1561-1</v>
       </c>
       <c r="F83" t="str">
-        <v>087-843-3689</v>
+        <v>087-886-5879</v>
       </c>
       <c r="G83" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h163/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h39/</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5026,10 +5026,10 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>1号認定 15、2・3号認定 160</v>
+        <v>1号認定 15、2・3号認定 100</v>
       </c>
       <c r="M83" t="str">
-        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N83" t="str">
         <v>月火水木金土</v>
@@ -5044,30 +5044,30 @@
         <v/>
       </c>
       <c r="R83" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B84" t="str">
-        <v>34.326539</v>
+        <v>34.331077</v>
       </c>
       <c r="C84" t="str">
-        <v>134.047837</v>
+        <v>134.094275</v>
       </c>
       <c r="D84" t="str">
-        <v>認定こども園花ノ宮こども園</v>
+        <v>認定こども園春日こども園</v>
       </c>
       <c r="E84" t="str">
-        <v>高松市花ノ宮町一丁目10-22</v>
+        <v>高松市春日町1287-1</v>
       </c>
       <c r="F84" t="str">
-        <v>087-831-6318</v>
+        <v>087-843-3689</v>
       </c>
       <c r="G84" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h175/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h163/</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -5082,7 +5082,7 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>1号認定 15、2・3号認定 110</v>
+        <v>1号認定 15、2・3号認定 160</v>
       </c>
       <c r="M84" t="str">
         <v>1号認定 3歳児～、2・3号認定 2か月～</v>
@@ -5100,30 +5100,30 @@
         <v/>
       </c>
       <c r="R84" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B85" t="str">
-        <v>34.333461</v>
+        <v>34.326539</v>
       </c>
       <c r="C85" t="str">
-        <v>134.04506</v>
+        <v>134.047837</v>
       </c>
       <c r="D85" t="str">
-        <v>認定こども園中野保育所</v>
+        <v>認定こども園花ノ宮こども園</v>
       </c>
       <c r="E85" t="str">
-        <v>高松市中野町27-5</v>
+        <v>高松市花ノ宮町一丁目10-22</v>
       </c>
       <c r="F85" t="str">
-        <v>087-831-8659</v>
+        <v>087-831-6318</v>
       </c>
       <c r="G85" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h174/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h175/</v>
       </c>
       <c r="H85" t="str">
         <v/>
@@ -5138,48 +5138,48 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>1号認定 15、2・3号認定 160</v>
+        <v>1号認定 15、2・3号認定 110</v>
       </c>
       <c r="M85" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
       </c>
       <c r="N85" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O85" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P85" t="str">
-        <v>19:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q85" t="str">
         <v/>
       </c>
       <c r="R85" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B86" t="str">
-        <v>34.279891</v>
+        <v>34.333461</v>
       </c>
       <c r="C86" t="str">
-        <v>134.042395</v>
+        <v>134.04506</v>
       </c>
       <c r="D86" t="str">
-        <v>幼保連携型認定こども園カナン保育園</v>
+        <v>認定こども園中野保育所</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市仏生山町甲745-2</v>
+        <v>高松市中野町27-5</v>
       </c>
       <c r="F86" t="str">
-        <v>087-889-1059</v>
+        <v>087-831-8659</v>
       </c>
       <c r="G86" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h166/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h174/</v>
       </c>
       <c r="H86" t="str">
         <v/>
@@ -5194,48 +5194,48 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>1号認定 15、2・3号認定 160</v>
       </c>
       <c r="M86" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 満3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N86" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O86" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P86" t="str">
-        <v>19:00</v>
+        <v>19:30</v>
       </c>
       <c r="Q86" t="str">
         <v/>
       </c>
       <c r="R86" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B87" t="str">
-        <v>34.292691</v>
+        <v>34.279891</v>
       </c>
       <c r="C87" t="str">
-        <v>134.0352</v>
+        <v>134.042395</v>
       </c>
       <c r="D87" t="str">
-        <v>幼保連携型認定こども園すまいる</v>
+        <v>幼保連携型認定こども園カナン保育園</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市三名町591-1</v>
+        <v>高松市仏生山町甲745-2</v>
       </c>
       <c r="F87" t="str">
-        <v>087-802-3838</v>
+        <v>087-889-1059</v>
       </c>
       <c r="G87" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h275/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h166/</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -5250,16 +5250,16 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>1号認定 75、2・3号認定 75</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M87" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 満3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N87" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O87" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P87" t="str">
         <v>19:00</v>
@@ -5268,30 +5268,30 @@
         <v/>
       </c>
       <c r="R87" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B88" t="str">
-        <v>34.2936161</v>
+        <v>34.292691</v>
       </c>
       <c r="C88" t="str">
-        <v>134.0789214</v>
+        <v>134.0352</v>
       </c>
       <c r="D88" t="str">
-        <v>げんき・結愛・げんきこども園</v>
+        <v>幼保連携型認定こども園すまいる</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市六条町604番地7</v>
+        <v>高松市三名町591-1</v>
       </c>
       <c r="F88" t="str">
-        <v>087-813-9818</v>
+        <v>087-802-3838</v>
       </c>
       <c r="G88" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h37/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h275/</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5306,16 +5306,16 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>1号認定 15、2・3号認定 217</v>
+        <v>1号認定 60、2・3号認定 130</v>
       </c>
       <c r="M88" t="str">
-        <v>1号認定 3歳児～、2・3号認定 おおむね2か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N88" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O88" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P88" t="str">
         <v>19:00</v>
@@ -5324,30 +5324,30 @@
         <v/>
       </c>
       <c r="R88" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B89" t="str">
-        <v>34.2734776</v>
+        <v>34.2936161</v>
       </c>
       <c r="C89" t="str">
-        <v>134.1024882</v>
+        <v>134.0789214</v>
       </c>
       <c r="D89" t="str">
-        <v>幼保連携型カナン十河こども園</v>
+        <v>げんき・結愛・げんきこども園</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市十川西町546-1</v>
+        <v>高松市六条町604番地7</v>
       </c>
       <c r="F89" t="str">
-        <v>087-848-0320</v>
+        <v>087-813-9818</v>
       </c>
       <c r="G89" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h48/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h37/</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5362,16 +5362,16 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>1号認定 15、2・3号認定 110</v>
+        <v>1号認定 15、2・3号認定 131</v>
       </c>
       <c r="M89" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 満3歳児～、2・3号認定 おおむね2か月～</v>
       </c>
       <c r="N89" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O89" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P89" t="str">
         <v>19:00</v>
@@ -5380,30 +5380,30 @@
         <v/>
       </c>
       <c r="R89" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" t="str">
-        <v>34.3064057</v>
+        <v>34.2734776</v>
       </c>
       <c r="C90" t="str">
-        <v>134.042294</v>
+        <v>134.1024882</v>
       </c>
       <c r="D90" t="str">
-        <v>幼保連携型認定こども園高松和貴こども園</v>
+        <v>幼保連携型カナン十河こども園</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市林町2197-1</v>
+        <v>高松市十川西町546-1</v>
       </c>
       <c r="F90" t="str">
-        <v>087-814-4141</v>
+        <v>087-848-0320</v>
       </c>
       <c r="G90" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h313/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h48/</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -5418,16 +5418,16 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>1号認定 15、2・3号認定 165</v>
+        <v>1号認定 15、2・3号認定 110</v>
       </c>
       <c r="M90" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 おおむね3か月～</v>
       </c>
       <c r="N90" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O90" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P90" t="str">
         <v>19:00</v>
@@ -5436,30 +5436,30 @@
         <v/>
       </c>
       <c r="R90" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B91" t="str">
-        <v>34.3264572</v>
+        <v>34.3064057</v>
       </c>
       <c r="C91" t="str">
-        <v>134.0769366</v>
+        <v>134.042294</v>
       </c>
       <c r="D91" t="str">
-        <v>みらい学園</v>
+        <v>幼保連携型認定こども園高松和貴こども園</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市木太町3429-3</v>
+        <v>高松市林町2197-1</v>
       </c>
       <c r="F91" t="str">
-        <v>087-899-2305</v>
+        <v>087-814-4141</v>
       </c>
       <c r="G91" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h313/</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5474,16 +5474,16 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>1号認定 15、2・3号認定 75</v>
+        <v>1号認定 15、2・3号認定 165</v>
       </c>
       <c r="M91" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N91" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O91" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P91" t="str">
         <v>19:00</v>
@@ -5497,31 +5497,31 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B92" t="str">
-        <v>34.353781</v>
+        <v>34.3264572</v>
       </c>
       <c r="C92" t="str">
-        <v>134.091115</v>
+        <v>134.0769366</v>
       </c>
       <c r="D92" t="str">
-        <v>認定こども園やしま幼稚園</v>
+        <v>みらい学園</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市屋島西町2477-4</v>
+        <v>高松市木太町3429-3</v>
       </c>
       <c r="F92" t="str">
-        <v>087-843-2241</v>
+        <v>087-899-2305</v>
       </c>
       <c r="G92" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h149</v>
+        <v/>
       </c>
       <c r="H92" t="str">
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>認定こども園（幼稚園型）</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5530,16 +5530,16 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>1号認定 228、2・3号認定 72</v>
+        <v>1号認定 15、2・3号認定 75</v>
       </c>
       <c r="M92" t="str">
-        <v>1号認定 満3歳～、2・3号認定 18か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N92" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O92" t="str">
-        <v>07:45</v>
+        <v>07:30</v>
       </c>
       <c r="P92" t="str">
         <v>19:00</v>
@@ -5553,25 +5553,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B93" t="str">
-        <v>34.338923</v>
+        <v>34.353781</v>
       </c>
       <c r="C93" t="str">
-        <v>134.031483</v>
+        <v>134.091115</v>
       </c>
       <c r="D93" t="str">
-        <v>高松聖ヤコブ幼稚園</v>
+        <v>認定こども園やしま幼稚園</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市西宝町二丁目3-14</v>
+        <v>高松市屋島西町2477-4</v>
       </c>
       <c r="F93" t="str">
-        <v>087-861-0425</v>
+        <v>087-843-2241</v>
       </c>
       <c r="G93" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h249</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h149</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5586,19 +5586,19 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>1号認定 135、2号認定 15</v>
+        <v>1号認定 120、2・3号認定 120</v>
       </c>
       <c r="M93" t="str">
-        <v>1号認定 満3歳～、2号認定 3歳児～</v>
+        <v>1号認定 満3歳～、2・3号認定 14か月～</v>
       </c>
       <c r="N93" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O93" t="str">
-        <v>07:30</v>
+        <v>07:45</v>
       </c>
       <c r="P93" t="str">
-        <v>18:30</v>
+        <v>18:45</v>
       </c>
       <c r="Q93" t="str">
         <v/>
@@ -5609,25 +5609,25 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B94" t="str">
-        <v>34.338702</v>
+        <v>34.338923</v>
       </c>
       <c r="C94" t="str">
-        <v>134.038281</v>
+        <v>134.031483</v>
       </c>
       <c r="D94" t="str">
-        <v>認定こども園亀阜幼稚園</v>
+        <v>高松聖ヤコブ幼稚園</v>
       </c>
       <c r="E94" t="str">
-        <v>宮脇町一丁目2-23</v>
+        <v>高松市西宝町二丁目3-14</v>
       </c>
       <c r="F94" t="str">
-        <v>087-831-2557</v>
+        <v>087-861-0425</v>
       </c>
       <c r="G94" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h252</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h249</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5642,10 +5642,10 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>1号認定 109、2・3号認定 99</v>
+        <v>1号認定 130、2号認定 20</v>
       </c>
       <c r="M94" t="str">
-        <v>1号認定 満3歳～、2・3号認定 1歳児～</v>
+        <v>1号認定 満3歳～、2号認定 3歳児～</v>
       </c>
       <c r="N94" t="str">
         <v>月火水木金土</v>
@@ -5654,7 +5654,7 @@
         <v>07:30</v>
       </c>
       <c r="P94" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q94" t="str">
         <v/>
@@ -5665,25 +5665,25 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B95" t="str">
-        <v>34.279836</v>
+        <v>34.338702</v>
       </c>
       <c r="C95" t="str">
-        <v>134.022373</v>
+        <v>134.038281</v>
       </c>
       <c r="D95" t="str">
-        <v>らく楽寺井幼稚園</v>
+        <v>認定こども園亀阜幼稚園</v>
       </c>
       <c r="E95" t="str">
-        <v>高松市寺井町1369-4</v>
+        <v>宮脇町一丁目2-23</v>
       </c>
       <c r="F95" t="str">
-        <v>087-885-2038</v>
+        <v>087-831-2557</v>
       </c>
       <c r="G95" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h264</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h252</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -5698,10 +5698,10 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>1号認定 112、2・3号認定 128</v>
+        <v>1号認定 109、2・3号認定 99</v>
       </c>
       <c r="M95" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 1歳児～</v>
       </c>
       <c r="N95" t="str">
         <v>月火水木金土</v>
@@ -5721,25 +5721,25 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B96" t="str">
-        <v>34.334019</v>
+        <v>34.279836</v>
       </c>
       <c r="C96" t="str">
-        <v>134.114815</v>
+        <v>134.022373</v>
       </c>
       <c r="D96" t="str">
-        <v>幼稚園型認定こども園つくし幼稚園</v>
+        <v>らく楽寺井幼稚園</v>
       </c>
       <c r="E96" t="str">
-        <v>高松市高松町1711-7</v>
+        <v>高松市寺井町1369-4</v>
       </c>
       <c r="F96" t="str">
-        <v>087-843-4484</v>
+        <v>087-885-2038</v>
       </c>
       <c r="G96" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h272/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h264</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -5754,10 +5754,10 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>1号認定 274、2・3号認定 48</v>
+        <v>1号認定 112、2・3号認定 128</v>
       </c>
       <c r="M96" t="str">
-        <v>1号認定 満3歳～、2・3号認定 2歳児～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N96" t="str">
         <v>月火水木金土</v>
@@ -5777,25 +5777,25 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B97" t="str">
-        <v>34.304505</v>
+        <v>34.334019</v>
       </c>
       <c r="C97" t="str">
-        <v>134.021922</v>
+        <v>134.114815</v>
       </c>
       <c r="D97" t="str">
-        <v>認定こども園勅使百華幼稚園</v>
+        <v>幼稚園型認定こども園つくし幼稚園</v>
       </c>
       <c r="E97" t="str">
-        <v>高松市勅使町955</v>
+        <v>高松市高松町1711-7</v>
       </c>
       <c r="F97" t="str">
-        <v>087-865-9419</v>
+        <v>087-843-4484</v>
       </c>
       <c r="G97" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h273/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h272/</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -5810,10 +5810,10 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>1号認定 265、2・3号認定 51</v>
+        <v>1号認定 150、2・3号認定 110</v>
       </c>
       <c r="M97" t="str">
-        <v>1号認定 満3歳～、2・3号認定 18か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 15か月～</v>
       </c>
       <c r="N97" t="str">
         <v>月火水木金土</v>
@@ -5822,42 +5822,42 @@
         <v>07:30</v>
       </c>
       <c r="P97" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q97" t="str">
         <v/>
       </c>
       <c r="R97" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98" t="str">
-        <v>34.235856</v>
+        <v>34.304505</v>
       </c>
       <c r="C98" t="str">
-        <v>133.994046</v>
+        <v>134.021922</v>
       </c>
       <c r="D98" t="str">
-        <v>カナン空港こども園</v>
+        <v>認定こども園勅使百華幼稚園</v>
       </c>
       <c r="E98" t="str">
-        <v>高松市香南町西庄1671-2</v>
+        <v>高松市勅使町955</v>
       </c>
       <c r="F98" t="str">
-        <v>087-815-8072</v>
+        <v>087-865-9419</v>
       </c>
       <c r="G98" t="str">
-        <v>https://kagawa-colorful.com/%253Fpage_id%253D3202</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h273/</v>
       </c>
       <c r="H98" t="str">
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>地域型保育事業（小規模保育事業A型）</v>
+        <v>認定こども園（幼稚園型）</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -5866,19 +5866,19 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>18</v>
+        <v>1号認定 217、2・3号認定 99</v>
       </c>
       <c r="M98" t="str">
-        <v>3か月～2歳児</v>
+        <v>1号認定 満3歳～、2・3号認定 16か月～（4.1時点1歳児）</v>
       </c>
       <c r="N98" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O98" t="str">
-        <v>07:15</v>
+        <v>07:30</v>
       </c>
       <c r="P98" t="str">
-        <v>18:15</v>
+        <v>18:30</v>
       </c>
       <c r="Q98" t="str">
         <v/>
@@ -5978,7 +5978,7 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M100" t="str">
         <v>2か月～2歳児</v>
@@ -6046,7 +6046,7 @@
         <v>07:30</v>
       </c>
       <c r="P101" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q101" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>ソラ小規模保育園たかまつ</v>
       </c>
       <c r="E102" t="str">
-        <v>高松市木太町786-2</v>
+        <v>高松市木太町9区786-2</v>
       </c>
       <c r="F102" t="str">
         <v>087-816-5150</v>
@@ -6261,7 +6261,7 @@
         <v>11</v>
       </c>
       <c r="M105" t="str">
-        <v>おおむね2か月～2歳児</v>
+        <v>おおむね3か月～2歳児</v>
       </c>
       <c r="N105" t="str">
         <v>月火水木金土</v>
@@ -6332,7 +6332,7 @@
         <v/>
       </c>
       <c r="R106" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="107">
@@ -6626,7 +6626,7 @@
         <v>134.0367875</v>
       </c>
       <c r="D112" t="str">
-        <v>保育の家みいろ</v>
+        <v>みいろ</v>
       </c>
       <c r="E112" t="str">
         <v>高松市香川町浅野668-5</v>
@@ -6738,16 +6738,16 @@
         <v>134.044986</v>
       </c>
       <c r="D114" t="str">
-        <v>院内保育所てふてふ</v>
+        <v>保育所てふてふ</v>
       </c>
       <c r="E114" t="str">
-        <v>高松市天神前5-6 高松メディカルモール</v>
+        <v>高松市天神前5-6 高松メディカルモール2階・4階</v>
       </c>
       <c r="F114" t="str">
         <v>087-813-0218</v>
       </c>
       <c r="G114" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%25E9%2599%25A2%25E5%2586%2585%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25E3%2580%2580%25E3%2581%25A6%25E3%2581%25B5%25E3%2581%25A6%25E3%2581%25B5/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/院内保育所　てふてふ/</v>
       </c>
       <c r="H114" t="str">
         <v/>
@@ -6774,7 +6774,7 @@
         <v>07:30</v>
       </c>
       <c r="P114" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q114" t="str">
         <v/>
@@ -6788,28 +6788,28 @@
         <v>121</v>
       </c>
       <c r="B115" t="str">
-        <v>34.30287</v>
+        <v>34.31871165074609</v>
       </c>
       <c r="C115" t="str">
-        <v>134.016075</v>
+        <v>134.04616290974917</v>
       </c>
       <c r="D115" t="str">
-        <v>メリーＧＯランド高松園</v>
+        <v>小規模保育施設おひさま保育園</v>
       </c>
       <c r="E115" t="str">
-        <v>高松市成合町796-1</v>
+        <v xml:space="preserve">高松市三条町４９４番地１　</v>
       </c>
       <c r="F115" t="str">
-        <v>087-886-6669</v>
+        <v>087-899-5565</v>
       </c>
       <c r="G115" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h274/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　小規模保育施設おひさま保育園/</v>
       </c>
       <c r="H115" t="str">
         <v/>
       </c>
       <c r="I115" t="str">
-        <v>認定こども園（地方裁量型）</v>
+        <v>地域型保育事業（事業所内保育事業）</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -6818,10 +6818,10 @@
         <v/>
       </c>
       <c r="L115" t="str">
-        <v>1号認定 20、2・3号認定 35</v>
+        <v>18</v>
       </c>
       <c r="M115" t="str">
-        <v>1号認定 満3歳～、2・3号認定 1歳半～</v>
+        <v>おおむね３か月～2歳児</v>
       </c>
       <c r="N115" t="str">
         <v>月火水木金土</v>
@@ -6830,7 +6830,7 @@
         <v>07:30</v>
       </c>
       <c r="P115" t="str">
-        <v>18:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q115" t="str">
         <v/>
@@ -6839,9 +6839,289 @@
         <v>無</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>122</v>
+      </c>
+      <c r="B116" t="str">
+        <v>34.297299240412265</v>
+      </c>
+      <c r="C116" t="str">
+        <v>134.0574624385844</v>
+      </c>
+      <c r="D116" t="str">
+        <v>スマはぴ保育園　なないろstation</v>
+      </c>
+      <c r="E116" t="str">
+        <v xml:space="preserve">高松市多肥上町１３０1番地３　</v>
+      </c>
+      <c r="F116" t="str">
+        <v>090-2373-7716</v>
+      </c>
+      <c r="G116" t="str">
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　スマはぴ保育園なないろstation/</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>地域型保育事業（事業所内保育事業）</v>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v>18</v>
+      </c>
+      <c r="M116" t="str">
+        <v>３か月～2歳児</v>
+      </c>
+      <c r="N116" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O116" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P116" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v>有</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>123</v>
+      </c>
+      <c r="B117" t="str">
+        <v>34.309844386262995</v>
+      </c>
+      <c r="C117" t="str">
+        <v>134.04623465392953</v>
+      </c>
+      <c r="D117" t="str">
+        <v>にこにこ保育教育研究センター　附属保育園すくすく</v>
+      </c>
+      <c r="E117" t="str">
+        <v>高松市太田下町２３５０番地１</v>
+      </c>
+      <c r="F117" t="str">
+        <v>087-802-5361</v>
+      </c>
+      <c r="G117" t="str">
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園すくすく/</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>地域型保育事業（事業所内保育事業）</v>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
+        <v>19</v>
+      </c>
+      <c r="M117" t="str">
+        <v>おおむね2か月～2歳児</v>
+      </c>
+      <c r="N117" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O117" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P117" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v>有</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>124</v>
+      </c>
+      <c r="B118" t="str">
+        <v>34.3097729899615</v>
+      </c>
+      <c r="C118" t="str">
+        <v>134.0461698809127</v>
+      </c>
+      <c r="D118" t="str">
+        <v>にこにこ保育教育研究センター　附属保育園わくわく</v>
+      </c>
+      <c r="E118" t="str">
+        <v>高松市太田下町２３５０番地１</v>
+      </c>
+      <c r="F118" t="str">
+        <v>087-802-5362</v>
+      </c>
+      <c r="G118" t="str">
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園わくわく/</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v>地域型保育事業（事業所内保育事業）</v>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v>19</v>
+      </c>
+      <c r="M118" t="str">
+        <v>おおむね2か月～2歳児</v>
+      </c>
+      <c r="N118" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O118" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P118" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v>有</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>125</v>
+      </c>
+      <c r="B119" t="str">
+        <v>34.27968265221049</v>
+      </c>
+      <c r="C119" t="str">
+        <v>134.02278072883618</v>
+      </c>
+      <c r="D119" t="str">
+        <v>らく楽寺井保育園</v>
+      </c>
+      <c r="E119" t="str">
+        <v>高松市寺井町１３６４番地２５</v>
+      </c>
+      <c r="F119" t="str">
+        <v>087-885-6002</v>
+      </c>
+      <c r="G119" t="str">
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　らく楽寺井保育園/</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v>地域型保育事業（事業所内保育事業）</v>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v>18</v>
+      </c>
+      <c r="M119" t="str">
+        <v>３か月～2歳児</v>
+      </c>
+      <c r="N119" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O119" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P119" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v>無</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>126</v>
+      </c>
+      <c r="B120" t="str">
+        <v>34.30287</v>
+      </c>
+      <c r="C120" t="str">
+        <v>134.016075</v>
+      </c>
+      <c r="D120" t="str">
+        <v>メリーＧＯランド高松園</v>
+      </c>
+      <c r="E120" t="str">
+        <v>高松市成合町796-1</v>
+      </c>
+      <c r="F120" t="str">
+        <v>087-886-6669</v>
+      </c>
+      <c r="G120" t="str">
+        <v>https://kagawa-colorful.com/hoikusyo/h274/</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>認定こども園（地方裁量型）</v>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v>1号認定 20、2・3号認定 35</v>
+      </c>
+      <c r="M120" t="str">
+        <v>1号認定 満3歳～、2・3号認定 1歳半～</v>
+      </c>
+      <c r="N120" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O120" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P120" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v>有</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R120"/>
   </ignoredErrors>
 </worksheet>
 </file>